--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:24</t>
+    <t xml:space="preserve">2026-09-09 23:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:21</t>
+    <t xml:space="preserve">2026-09-17 14:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:16</t>
+    <t xml:space="preserve">2026-09-23 12:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -600,7 +600,9 @@
       <c r="C8" s="2" t="n">
         <v>1403</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2" t="n">
+        <v>2018</v>
+      </c>
       <c r="E8" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_tarapaca.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:44</t>
+    <t xml:space="preserve">2026-10-01 23:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre la mediana nacional (%)</t>
+    <t xml:space="preserve">% bajo 50% de la mediana</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre mediana</t>
   </si>
 </sst>
 </file>
@@ -682,7 +679,7 @@
         <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:01</t>
+    <t xml:space="preserve">2026-10-02 11:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:17</t>
+    <t xml:space="preserve">2026-10-02 13:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:42</t>
+    <t xml:space="preserve">2026-10-05 11:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
